--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104467_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104467_W1.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2451</v>
+        <v>9.5778</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0136</v>
+        <v>8.413600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2316</v>
+        <v>1.1641</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1917</v>
+        <v>6.1862</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4849</v>
+        <v>0.4826</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7069</v>
+        <v>5.7036</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4279</v>
+        <v>6.3987</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6438</v>
+        <v>0.627</v>
       </c>
       <c r="L2" t="n">
-        <v>5.7841</v>
+        <v>5.7717</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2362</v>
+        <v>-0.2125</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8266</v>
+        <v>0.1639</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9467</v>
+        <v>0.3807</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1201</v>
+        <v>-0.2168</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9205</v>
+        <v>6.2626</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7006</v>
+        <v>4.9202</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2199</v>
+        <v>1.3425</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7071</v>
+        <v>3.7099</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7533</v>
+        <v>1.7493</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9539</v>
+        <v>1.9606</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5702</v>
+        <v>3.5501</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2268</v>
+        <v>2.2096</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M3" t="n">
-        <v>0.137</v>
+        <v>0.1598</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9185</v>
+        <v>0.2568</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8771</v>
+        <v>0.1228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0414</v>
+        <v>0.1339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6886</v>
+        <v>4.192</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1524</v>
+        <v>3.4398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5362</v>
+        <v>0.7522</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0983</v>
+        <v>2.1125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6535</v>
+        <v>0.6629</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4448</v>
+        <v>1.4496</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6626</v>
+        <v>1.6513</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1429</v>
+        <v>1.1376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4356</v>
+        <v>0.4613</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O4" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5685</v>
+        <v>-1.0799</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>-0.3904</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8729</v>
+        <v>-0.6895</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3398</v>
+        <v>2.2567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8993</v>
+        <v>0.7544</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4405</v>
+        <v>1.5023</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4591</v>
+        <v>1.4682</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2481</v>
+        <v>2.2515</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7889</v>
+        <v>-0.7833</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4821</v>
+        <v>1.4635</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2339</v>
+        <v>2.2236</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7517</v>
+        <v>-0.7601</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.023</v>
+        <v>0.0048</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1055</v>
+        <v>0.0177</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2299</v>
+        <v>0.1136</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1243</v>
+        <v>-0.0959</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3609</v>
+        <v>1.0879</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0476</v>
+        <v>2.2432</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6867</v>
+        <v>-1.1553</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3781</v>
+        <v>1.3921</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1835</v>
+        <v>-1.167</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5616</v>
+        <v>2.559</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1655</v>
+        <v>2.1506</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0097</v>
+        <v>1.9955</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7875</v>
+        <v>-0.7585</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0587</v>
+        <v>-0.3529</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1179</v>
+        <v>0.0926</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0593</v>
+        <v>-0.4455</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4429</v>
+        <v>0.7513</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.964</v>
+        <v>0.9264</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4069</v>
+        <v>-0.1751</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0273</v>
+        <v>-1.2432</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5741</v>
+        <v>-3.4837</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4532</v>
+        <v>2.2406</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2285</v>
+        <v>0.6048</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2685</v>
+        <v>-1.659</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04</v>
+        <v>2.2638</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2011</v>
+        <v>-1.848</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6944</v>
+        <v>-1.8248</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4932</v>
+        <v>-0.0232</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.4025</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5646</v>
+        <v>-0.3227</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0907</v>
+        <v>-0.1745</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4739</v>
+        <v>-0.1482</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4141</v>
+        <v>0.2432</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3744</v>
+        <v>-0.9787</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0397</v>
+        <v>1.2219</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2454</v>
+        <v>2.0443</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.4818</v>
+        <v>1.5821</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2364</v>
+        <v>0.4622</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6347</v>
+        <v>2.2131</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6389</v>
+        <v>2.258</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2736</v>
+        <v>-0.0449</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8801</v>
+        <v>-0.1689</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8429</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0372</v>
+        <v>0.5071</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6599</v>
+        <v>0.3662</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>0.1136</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1052</v>
+        <v>0.2526</v>
       </c>
       <c r="V8" t="n">
-        <v>1.639</v>
+        <v>1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>1.639</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.529</v>
+        <v>-0.797</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1696</v>
+        <v>-1.0811</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6986</v>
+        <v>0.2841</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6257</v>
+        <v>1.4351</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7994</v>
+        <v>0.4477</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8263</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7144</v>
+        <v>0.1409</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7517</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0515</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9113</v>
+        <v>1.2942</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0477</v>
+        <v>0.3583</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8636</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1382</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.598</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.0838</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.5141</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.6342</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>0.4537</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.1963</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.2087</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.1607</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.0927</v>
-      </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8885</v>
+        <v>-1.0068</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.736</v>
+        <v>0.7059</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1525</v>
+        <v>-1.7127</v>
       </c>
       <c r="G10" t="n">
-        <v>1.433</v>
+        <v>-1.619</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4414</v>
+        <v>-0.7985</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9915</v>
+        <v>-0.8205</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1633</v>
+        <v>-0.7179</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0968</v>
+        <v>-0.7552</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0665</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2697</v>
+        <v>-0.9011</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3446</v>
+        <v>-0.0433</v>
       </c>
       <c r="O10" t="n">
-        <v>0.925</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.1342</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6825</v>
+        <v>0.3148</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7652</v>
+        <v>0.3344</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9173</v>
+        <v>-0.0196</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.639</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8756</v>
+        <v>-2.2398</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9219</v>
+        <v>-3.5339</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0463</v>
+        <v>1.2941</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6272</v>
+        <v>-0.6204</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8743</v>
+        <v>-2.8776</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2471</v>
+        <v>2.2572</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8469</v>
+        <v>-0.8673</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2276</v>
+        <v>-2.245</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3807</v>
+        <v>1.3778</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2197</v>
+        <v>0.2468</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6172</v>
+        <v>-0.9789</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>-0.3417</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.852</v>
+        <v>-0.6372</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.756</v>
+        <v>-4.9031</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7638</v>
+        <v>-5.0844</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0077</v>
+        <v>0.1814</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8122</v>
+        <v>-1.8171</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6522</v>
+        <v>-1.6515</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.16</v>
+        <v>-0.1656</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6823</v>
+        <v>-1.7044</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2264</v>
+        <v>-1.2345</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4559</v>
+        <v>-0.4698</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1299</v>
+        <v>-0.1127</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8363</v>
+        <v>-0.9674</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1603</v>
+        <v>-0.1233</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9966</v>
+        <v>-0.8441</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3628</v>
+        <v>15.4248</v>
       </c>
       <c r="E13" t="n">
-        <v>9.971800000000002</v>
+        <v>10.7254</v>
       </c>
       <c r="F13" t="n">
-        <v>4.391</v>
+        <v>4.6995</v>
       </c>
       <c r="G13" t="n">
-        <v>12.9841</v>
+        <v>13.0486</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8359</v>
+        <v>-2.8022</v>
       </c>
       <c r="I13" t="n">
-        <v>15.8202</v>
+        <v>15.8508</v>
       </c>
       <c r="J13" t="n">
-        <v>15.0912</v>
+        <v>14.8834</v>
       </c>
       <c r="K13" t="n">
-        <v>2.924</v>
+        <v>2.806599999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>12.1674</v>
+        <v>12.0768</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1071</v>
+        <v>-1.8348</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.7599</v>
+        <v>-5.608700000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6527</v>
+        <v>3.7743</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1341</v>
+        <v>-1.137999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7443</v>
+        <v>-14.7962</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6101</v>
+        <v>13.6581</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.2042</v>
+        <v>-3.1804</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0131</v>
+        <v>0.04399999999999989</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.191</v>
+        <v>-3.2244</v>
       </c>
       <c r="V13" t="n">
-        <v>6.7167</v>
+        <v>6.6945</v>
       </c>
       <c r="W13" t="n">
-        <v>10.6376</v>
+        <v>10.594</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.9209</v>
+        <v>-3.8995</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5622</v>
+        <v>4.2529</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7245</v>
+        <v>1.9743</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8378</v>
+        <v>2.2786</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5441</v>
+        <v>2.531</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2741</v>
+        <v>4.2682</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.73</v>
+        <v>-1.7372</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1535</v>
+        <v>3.1159</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4331</v>
+        <v>4.4126</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2796</v>
+        <v>-1.2967</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.5849</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2015</v>
+        <v>0.9024</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3157</v>
+        <v>0.6127</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8858</v>
+        <v>0.2897</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6979</v>
+        <v>1.2882</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3252</v>
+        <v>2.8373</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6273</v>
+        <v>-1.5491</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7643</v>
+        <v>-0.7628</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2641</v>
+        <v>1.2583</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0284</v>
+        <v>-2.0211</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2824</v>
+        <v>1.2698</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0467</v>
+        <v>-2.0326</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1404</v>
+        <v>-2.1328</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0912</v>
+        <v>0.6851</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0162</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.075</v>
+        <v>0.1372</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1441</v>
+        <v>1.1383</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3863</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5515</v>
+        <v>0.9886</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1652</v>
+        <v>-0.104</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9275</v>
+        <v>-1.9366</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9913</v>
+        <v>0.9909</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.9188</v>
+        <v>-2.9275</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2145</v>
+        <v>-0.249</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5053</v>
+        <v>0.4891</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.713</v>
+        <v>-1.6876</v>
       </c>
       <c r="N16" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.199</v>
+        <v>-2.1893</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2574</v>
+        <v>0.2473</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0998</v>
+        <v>0.3758</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1576</v>
+        <v>-0.1286</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1689</v>
+        <v>0.2177</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8475</v>
+        <v>-0.9728</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0164</v>
+        <v>1.1905</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0364</v>
+        <v>-1.0308</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7561</v>
+        <v>-1.7549</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7197</v>
+        <v>0.7241</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0078</v>
+        <v>-1.0167</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1571</v>
+        <v>-1.1656</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0285</v>
+        <v>-0.0141</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3826</v>
+        <v>-0.345</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1603</v>
+        <v>0.0439</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5429</v>
+        <v>-0.3888</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4685</v>
+        <v>-1.1906</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0663</v>
+        <v>-0.0298</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4022</v>
+        <v>-1.1608</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4751</v>
+        <v>2.0976</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0806</v>
+        <v>2.6279</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3945</v>
+        <v>-0.5303</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5079</v>
+        <v>3.3852</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5452</v>
+        <v>3.1026</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.2826</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.2876</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5354</v>
+        <v>-0.4747</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4318</v>
+        <v>-0.8129</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1407</v>
+        <v>-0.1988</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0294</v>
+        <v>-0.0005</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1113</v>
+        <v>-0.1983</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5463</v>
+        <v>-2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5868</v>
+        <v>-1.7099</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2313</v>
+        <v>-1.379</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3555</v>
+        <v>-0.3309</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0972</v>
+        <v>-2.482</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6276</v>
+        <v>-2.0903</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5304</v>
+        <v>-0.3916</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4101</v>
+        <v>-1.5216</v>
       </c>
       <c r="K19" t="n">
-        <v>3.117</v>
+        <v>-1.5588</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2931</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.313</v>
+        <v>-0.9604</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4894</v>
+        <v>-0.5315</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8236</v>
+        <v>-0.4289</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5913</v>
+        <v>0.9103</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2389</v>
+        <v>0.736</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3524</v>
+        <v>0.1743</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1853</v>
+        <v>0.5447</v>
       </c>
       <c r="W19" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-2.1853</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5154</v>
+        <v>-2.0684</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8509</v>
+        <v>-1.5311</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6645</v>
+        <v>-0.5373</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7481</v>
+        <v>-1.7564</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1874</v>
+        <v>-3.1907</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4393</v>
+        <v>1.4343</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1633</v>
+        <v>-0.1951</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2103</v>
+        <v>-2.2278</v>
       </c>
       <c r="L20" t="n">
-        <v>2.047</v>
+        <v>2.0327</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5848</v>
+        <v>-1.5613</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3366</v>
+        <v>0.1125</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3266</v>
+        <v>0.0297</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.01</v>
+        <v>0.0827</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4307</v>
+        <v>-0.4245</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4307</v>
+        <v>-0.4245</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6945</v>
+        <v>-2.3943</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2212</v>
+        <v>0.6838</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9157</v>
+        <v>-3.0781</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2747</v>
+        <v>-2.2665</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4068</v>
+        <v>0.4132</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6815</v>
+        <v>-2.6797</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4087</v>
+        <v>0.3962</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6754</v>
+        <v>0.6722</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6834</v>
+        <v>-2.6628</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4149</v>
+        <v>-2.4037</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5553</v>
+        <v>0.843</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0393</v>
+        <v>0.5152</v>
       </c>
       <c r="U21" t="n">
-        <v>0.516</v>
+        <v>0.3278</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9946</v>
+        <v>-3.4926</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7678</v>
+        <v>-4.1717</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7732</v>
+        <v>0.679</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5879</v>
+        <v>-1.6009</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4284</v>
+        <v>-0.4389</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1595</v>
+        <v>-1.162</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3067</v>
+        <v>-0.3422</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1865</v>
+        <v>0.1649</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2812</v>
+        <v>-1.2587</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1565</v>
+        <v>0.6805</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5293</v>
+        <v>0.1784</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6273</v>
+        <v>0.5021</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7682</v>
+        <v>-4.7219</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8411</v>
+        <v>-0.9146</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9271</v>
+        <v>-3.8073</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6239</v>
+        <v>-2.6267</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4834</v>
+        <v>-0.4798</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1405</v>
+        <v>-2.1468</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9186</v>
+        <v>-0.9375</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3881</v>
+        <v>-0.3932</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7053</v>
+        <v>-1.6891</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5302</v>
+        <v>0.5097</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6956</v>
+        <v>0.2505</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1654</v>
+        <v>0.2592</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.8409</v>
+        <v>-2.8326</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.8409</v>
+        <v>-2.8326</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1501</v>
+        <v>-5.4448</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7012</v>
+        <v>-3.2739</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4489</v>
+        <v>-2.1709</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1877</v>
+        <v>-3.2148</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2079</v>
+        <v>1.1982</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.3956</v>
+        <v>-4.413</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0287</v>
+        <v>-2.0704</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9728</v>
+        <v>0.9545</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.0016</v>
+        <v>-3.025</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.159</v>
+        <v>-1.1444</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.1209</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5383</v>
+        <v>-0.0653</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3049</v>
+        <v>-0.0556</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.3628</v>
+        <v>-14.3791</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.483700000000001</v>
+        <v>-5.7889</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.879</v>
+        <v>-8.590299999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-12.9843</v>
+        <v>-13.0489</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8359</v>
+        <v>2.8021</v>
       </c>
       <c r="I25" t="n">
-        <v>-15.8202</v>
+        <v>-15.8508</v>
       </c>
       <c r="J25" t="n">
-        <v>2.1072</v>
+        <v>1.8346</v>
       </c>
       <c r="K25" t="n">
-        <v>5.7598</v>
+        <v>5.608600000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.652699999999999</v>
+        <v>-3.7742</v>
       </c>
       <c r="M25" t="n">
-        <v>-15.0915</v>
+        <v>-14.8835</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.9239</v>
+        <v>-2.8064</v>
       </c>
       <c r="O25" t="n">
-        <v>-12.1675</v>
+        <v>-12.0768</v>
       </c>
       <c r="P25" t="n">
-        <v>1.134</v>
+        <v>1.137999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R25" t="n">
-        <v>14.7443</v>
+        <v>14.7962</v>
       </c>
       <c r="S25" t="n">
-        <v>4.203900000000001</v>
+        <v>4.2261</v>
       </c>
       <c r="T25" t="n">
-        <v>3.191</v>
+        <v>3.2243</v>
       </c>
       <c r="U25" t="n">
-        <v>1.013</v>
+        <v>1.0017</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.716699999999999</v>
+        <v>-6.6945</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8282</v>
+        <v>2.8099</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.5449</v>
+        <v>-9.5045</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104467_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104467_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-3.8995</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.8326</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104467_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-9.5045</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
